--- a/app/zen_rules/Bank_Eligibility_Matrix_v1.xlsx
+++ b/app/zen_rules/Bank_Eligibility_Matrix_v1.xlsx
@@ -352,13 +352,13 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1065,7 +1065,7 @@
         <v>70</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>67</v>
@@ -1252,8 +1252,8 @@
       <c r="L3" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="M3" s="12" t="s">
-        <v>67</v>
+      <c r="M3" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="N3" s="12" t="s">
         <v>67</v>
@@ -1441,7 +1441,7 @@
         <v>86</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>67</v>
@@ -1628,8 +1628,8 @@
       <c r="L5" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="M5" s="12" t="s">
-        <v>67</v>
+      <c r="M5" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="N5" s="12" t="s">
         <v>67</v>
@@ -1816,8 +1816,8 @@
       <c r="L6" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="M6" s="12" t="s">
-        <v>67</v>
+      <c r="M6" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="N6" s="12" t="s">
         <v>67</v>
@@ -2005,7 +2005,7 @@
         <v>86</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N7" s="8" t="s">
         <v>67</v>
@@ -2192,8 +2192,8 @@
       <c r="L8" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="M8" s="12" t="s">
-        <v>67</v>
+      <c r="M8" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>67</v>
@@ -2381,7 +2381,7 @@
         <v>86</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>67</v>
